--- a/data/2025/sectors_2025.xlsx
+++ b/data/2025/sectors_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naughtm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB35D0C-823F-4683-880B-57F21933F959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F350F6E-DA79-4054-8964-E7AD9DBFD265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{386F7583-D0BB-4E66-BF93-DABCDAE51CFC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>January</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t xml:space="preserve">No Sector Entered </t>
+  </si>
+  <si>
+    <t>Economic Sector</t>
   </si>
 </sst>
 </file>
@@ -590,7 +593,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1797,6 +1802,54 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </m02c691f3efa402dab5cbaa8c240a9e7>
+    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Value>5</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
+    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
+        </TermInfo>
+      </Terms>
+    </h1f8bb4843d6459a8b809123185593c7>
+    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </fbaa881fc4ae443f9fdafbdd527793df>
+    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </nb1b8a72855341e18dd75ce464e281f2>
+    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
+        </TermInfo>
+      </Terms>
+    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -2005,68 +2058,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </m02c691f3efa402dab5cbaa8c240a9e7>
-    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Value>5</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
-    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
-        </TermInfo>
-      </Terms>
-    </h1f8bb4843d6459a8b809123185593c7>
-    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </fbaa881fc4ae443f9fdafbdd527793df>
-    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </nb1b8a72855341e18dd75ce464e281f2>
-    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
-        </TermInfo>
-      </Terms>
-    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B026853-42BE-421B-954B-6C59C283362C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B24E7EE8-BC93-43C4-AF57-03987B34B0DE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2088,9 +2083,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B24E7EE8-BC93-43C4-AF57-03987B34B0DE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B026853-42BE-421B-954B-6C59C283362C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>